--- a/assets/libreoffice_calc_njc/55b85705-22a1-4ed1-abf4-686015978529/WeeklyRevenue_AddProfit.xlsx
+++ b/assets/libreoffice_calc_njc/55b85705-22a1-4ed1-abf4-686015978529/WeeklyRevenue_AddProfit.xlsx
@@ -137,8 +137,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -160,168 +164,168 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>85000</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>62000</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <f aca="false">B2-C2</f>
         <v>23000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>92000</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>68000</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <f aca="false">B3-C3</f>
         <v>24000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>78000</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>55000</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <f aca="false">B4-C4</f>
         <v>23000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>95000</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>70000</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <f aca="false">B5-C5</f>
         <v>25000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>88000</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>64000</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <f aca="false">B6-C6</f>
         <v>24000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>103000</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>76000</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <f aca="false">B7-C7</f>
         <v>27000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>91000</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>67000</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <f aca="false">B8-C8</f>
         <v>24000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>97000</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>72000</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <f aca="false">B9-C9</f>
         <v>25000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>84000</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>60000</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <f aca="false">B10-C10</f>
         <v>24000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>82000</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <f aca="false">B11-C11</f>
         <v>28000</v>
       </c>
